--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F467946F-7EA8-43E1-9133-85EF9B75F603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5805EF5-37FF-4864-80FC-38BCB80D5830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name=" LMHSC-HRPP- VSLA-1 Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name=" LMHSC-HRPP- VSLA-1 Issues" sheetId="2" r:id="rId2"/>
+    <sheet name="VSLA-Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="VSLA-Issues" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -245,6 +245,40 @@
   </si>
   <si>
     <t xml:space="preserve">No-policy </t>
+  </si>
+  <si>
+    <t>KSFES-HRPP- VSLA-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rescue and Shift High risk pregnancy patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KSFES-HRPP- VSLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance Predictor/Advantage Predictor Equation with Alpha+
+Beta(i)+Beta(f) </t>
+  </si>
+  <si>
+    <t>Level3</t>
+  </si>
+  <si>
+    <t>Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unconnected-Risk </t>
+  </si>
+  <si>
+    <t>Provider-Fit;Patient-Fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSFES-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSFES-HRPP- VSLA </t>
+  </si>
+  <si>
+    <t>N-policy</t>
   </si>
 </sst>
 </file>
@@ -565,14 +599,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" customWidth="1"/>
     <col min="3" max="3" width="25.77734375" customWidth="1"/>
     <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="6" width="28.21875" customWidth="1"/>
+    <col min="5" max="5" width="28.21875" customWidth="1"/>
+    <col min="6" max="6" width="72.77734375" customWidth="1"/>
     <col min="7" max="7" width="18.77734375" customWidth="1"/>
     <col min="8" max="8" width="28.88671875" customWidth="1"/>
     <col min="9" max="9" width="54.44140625" customWidth="1"/>
@@ -754,6 +789,86 @@
         <v>61</v>
       </c>
     </row>
+    <row r="3" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T3" t="s">
+        <v>55</v>
+      </c>
+      <c r="U3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -761,7 +876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3375E5-3EC6-47D3-B579-FD7CAB2615C3}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -958,6 +1073,89 @@
         <v>72</v>
       </c>
     </row>
+    <row r="3" spans="1:27" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" t="s">
+        <v>83</v>
+      </c>
+      <c r="V3" t="s">
+        <v>77</v>
+      </c>
+      <c r="W3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5805EF5-37FF-4864-80FC-38BCB80D5830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ED737F-5ABA-448F-8F5B-10DEFB4928EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -279,6 +279,21 @@
   </si>
   <si>
     <t>N-policy</t>
+  </si>
+  <si>
+    <t>RVMETRO-HRPP- VSLA-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commute to and back for High risk pregnancy patient </t>
+  </si>
+  <si>
+    <t>RVMETRO-HRPP- VSLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Definite-Risk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RVMETRO-HRPP- VSLA-1 </t>
   </si>
 </sst>
 </file>
@@ -599,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -869,6 +884,86 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R4" t="s">
+        <v>87</v>
+      </c>
+      <c r="S4" t="s">
+        <v>54</v>
+      </c>
+      <c r="T4" t="s">
+        <v>55</v>
+      </c>
+      <c r="U4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -876,7 +971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3375E5-3EC6-47D3-B579-FD7CAB2615C3}">
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1156,6 +1251,89 @@
         <v>78</v>
       </c>
     </row>
+    <row r="4" spans="1:27" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O4" t="s">
+        <v>69</v>
+      </c>
+      <c r="P4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S4" t="s">
+        <v>77</v>
+      </c>
+      <c r="T4" t="s">
+        <v>77</v>
+      </c>
+      <c r="U4" t="s">
+        <v>83</v>
+      </c>
+      <c r="V4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W4" t="s">
+        <v>77</v>
+      </c>
+      <c r="X4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ED737F-5ABA-448F-8F5B-10DEFB4928EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B295B0E-55EB-4C6A-9194-0A339B2A6586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSLA-Dashboard" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -278,9 +278,6 @@
     <t xml:space="preserve">KSFES-HRPP- VSLA </t>
   </si>
   <si>
-    <t>N-policy</t>
-  </si>
-  <si>
     <t>RVMETRO-HRPP- VSLA-1</t>
   </si>
   <si>
@@ -294,6 +291,27 @@
   </si>
   <si>
     <t xml:space="preserve">RVMETRO-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCOBANK-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-loop commute for High risk pregnancy patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCOBANK-HRPP- VSLA </t>
+  </si>
+  <si>
+    <t>Leve2</t>
+  </si>
+  <si>
+    <t>No-policy</t>
+  </si>
+  <si>
+    <t>UCOBANK-HRPP- VSLA-1</t>
+  </si>
+  <si>
+    <t>UCIBANK-HRPP- VSLA</t>
   </si>
 </sst>
 </file>
@@ -614,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -886,16 +904,16 @@
     </row>
     <row r="4" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
         <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
@@ -934,10 +952,10 @@
         <v>48</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S4" t="s">
         <v>54</v>
@@ -961,6 +979,86 @@
         <v>60</v>
       </c>
       <c r="Z4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R5" t="s">
+        <v>79</v>
+      </c>
+      <c r="S5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" t="s">
+        <v>57</v>
+      </c>
+      <c r="W5" t="s">
+        <v>58</v>
+      </c>
+      <c r="X5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -971,12 +1069,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3375E5-3EC6-47D3-B579-FD7CAB2615C3}">
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" customWidth="1"/>
     <col min="4" max="4" width="22.109375" customWidth="1"/>
     <col min="5" max="5" width="20.109375" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
@@ -1230,7 +1328,7 @@
         <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="V3" t="s">
         <v>77</v>
@@ -1253,13 +1351,13 @@
     </row>
     <row r="4" spans="1:27" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
         <v>82</v>
@@ -1313,7 +1411,7 @@
         <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="V4" t="s">
         <v>77</v>
@@ -1332,6 +1430,89 @@
       </c>
       <c r="AA4" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" t="s">
+        <v>78</v>
+      </c>
+      <c r="T5" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" t="s">
+        <v>78</v>
+      </c>
+      <c r="W5" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B295B0E-55EB-4C6A-9194-0A339B2A6586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AD64DF-F211-4B97-947E-2A936B28701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSLA-Dashboard" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="99">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -311,7 +311,19 @@
     <t>UCOBANK-HRPP- VSLA-1</t>
   </si>
   <si>
-    <t>UCIBANK-HRPP- VSLA</t>
+    <t>EGANESHA-HRPP- VSLA-1</t>
+  </si>
+  <si>
+    <t>UCOBANK-HRPP- VSLA</t>
+  </si>
+  <si>
+    <t>EGANESHA-HRPP- VSLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGANESHA-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t>Level11</t>
   </si>
 </sst>
 </file>
@@ -632,12 +644,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
     <col min="4" max="4" width="20.21875" customWidth="1"/>
     <col min="5" max="5" width="28.21875" customWidth="1"/>
     <col min="6" max="6" width="72.77734375" customWidth="1"/>
@@ -993,7 +1005,7 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
@@ -1059,6 +1071,86 @@
         <v>60</v>
       </c>
       <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" t="s">
+        <v>79</v>
+      </c>
+      <c r="S6" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W6" t="s">
+        <v>58</v>
+      </c>
+      <c r="X6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1069,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3375E5-3EC6-47D3-B579-FD7CAB2615C3}">
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1515,6 +1607,89 @@
         <v>78</v>
       </c>
     </row>
+    <row r="6" spans="1:27" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U6" t="s">
+        <v>92</v>
+      </c>
+      <c r="V6" t="s">
+        <v>78</v>
+      </c>
+      <c r="W6" t="s">
+        <v>78</v>
+      </c>
+      <c r="X6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AD64DF-F211-4B97-947E-2A936B28701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C17ABD-75E5-4F57-93E0-A4AB67F7D920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="98">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -321,9 +321,6 @@
   </si>
   <si>
     <t xml:space="preserve">EGANESHA-HRPP- VSLA-1 </t>
-  </si>
-  <si>
-    <t>Level11</t>
   </si>
 </sst>
 </file>
@@ -1627,7 +1624,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
         <v>78</v>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C17ABD-75E5-4F57-93E0-A4AB67F7D920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8486FDD0-BB36-4C29-AB69-AA3EBCABEFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="104">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -302,9 +302,6 @@
     <t xml:space="preserve">UCOBANK-HRPP- VSLA </t>
   </si>
   <si>
-    <t>Leve2</t>
-  </si>
-  <si>
     <t>No-policy</t>
   </si>
   <si>
@@ -321,6 +318,28 @@
   </si>
   <si>
     <t xml:space="preserve">EGANESHA-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t>KALYANIMOTORS-HRPP- VSLA-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service vehicles used for commute for High risk pregnancy patient </t>
+  </si>
+  <si>
+    <t>KALYANIMOTORS-HRPP- VSLA</t>
+  </si>
+  <si>
+    <t>&lt;SQP-challenges&gt;;&lt;SQP-differentiation&gt;;&lt;SQP-capability&gt;; &lt;SQP
+human variability&gt;;&lt;SQP-non-compliant pretexts&gt;;&lt;SQP-Level-critical-path-probability-resolution&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KALYANIMOTORS-HRPP- VSLA-1 </t>
+  </si>
+  <si>
+    <t>Service vehicles used for commute for High risk pregnancy patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KALYANIMOTORS-HRPP- VSLA </t>
   </si>
 </sst>
 </file>
@@ -641,13 +660,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="3" max="3" width="61.21875" customWidth="1"/>
+    <col min="4" max="4" width="46.5546875" customWidth="1"/>
     <col min="5" max="5" width="28.21875" customWidth="1"/>
     <col min="6" max="6" width="72.77734375" customWidth="1"/>
     <col min="7" max="7" width="18.77734375" customWidth="1"/>
@@ -993,7 +1012,7 @@
     </row>
     <row r="5" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -1002,7 +1021,7 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
@@ -1041,7 +1060,7 @@
         <v>48</v>
       </c>
       <c r="Q5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R5" t="s">
         <v>79</v>
@@ -1073,7 +1092,7 @@
     </row>
     <row r="6" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -1082,7 +1101,7 @@
         <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>47</v>
@@ -1121,7 +1140,7 @@
         <v>48</v>
       </c>
       <c r="Q6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R6" t="s">
         <v>79</v>
@@ -1148,6 +1167,86 @@
         <v>60</v>
       </c>
       <c r="Z6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U7" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z7" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1158,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3375E5-3EC6-47D3-B579-FD7CAB2615C3}">
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1417,7 +1516,7 @@
         <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V3" t="s">
         <v>77</v>
@@ -1500,7 +1599,7 @@
         <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V4" t="s">
         <v>77</v>
@@ -1580,10 +1679,10 @@
         <v>78</v>
       </c>
       <c r="T5" t="s">
+        <v>78</v>
+      </c>
+      <c r="U5" t="s">
         <v>91</v>
-      </c>
-      <c r="U5" t="s">
-        <v>92</v>
       </c>
       <c r="V5" t="s">
         <v>78</v>
@@ -1606,7 +1705,7 @@
     </row>
     <row r="6" spans="1:27" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -1663,11 +1762,11 @@
         <v>78</v>
       </c>
       <c r="T6" t="s">
+        <v>78</v>
+      </c>
+      <c r="U6" t="s">
         <v>91</v>
       </c>
-      <c r="U6" t="s">
-        <v>92</v>
-      </c>
       <c r="V6" t="s">
         <v>78</v>
       </c>
@@ -1685,6 +1784,89 @@
       </c>
       <c r="AA6" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" t="s">
+        <v>78</v>
+      </c>
+      <c r="U7" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" t="s">
+        <v>78</v>
+      </c>
+      <c r="W7" t="s">
+        <v>78</v>
+      </c>
+      <c r="X7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8486FDD0-BB36-4C29-AB69-AA3EBCABEFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF45C087-9952-49EB-A656-E92C6E7BB9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSLA-Dashboard" sheetId="1" r:id="rId1"/>
     <sheet name="VSLA-Issues" sheetId="2" r:id="rId2"/>
+    <sheet name="VSLA-Testing" sheetId="3" r:id="rId3"/>
+    <sheet name="VSLA-Training" sheetId="4" r:id="rId4"/>
+    <sheet name="VSLA Process Improvement" sheetId="5" r:id="rId5"/>
+    <sheet name="RS&amp;A Intelligence and CQI" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="162">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -340,14 +344,196 @@
   </si>
   <si>
     <t xml:space="preserve">KALYANIMOTORS-HRPP- VSLA </t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>No dedicated Centre</t>
+  </si>
+  <si>
+    <t>RSA Package Subscription Type - GOVT/LINKED/ BOTH</t>
+  </si>
+  <si>
+    <t>Suraksha Centre QOS Testing Status</t>
+  </si>
+  <si>
+    <t>Suraksha Centre QOP Testing Status</t>
+  </si>
+  <si>
+    <t>Suraksha Centre QOO Testing Status</t>
+  </si>
+  <si>
+    <t>Suraksha Centre QODIL Testing Status</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>GOVT</t>
+  </si>
+  <si>
+    <t>Active-GOVT</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>NEXT Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSA Status - Basic (Level1)/                NEXT Step (Level2)/              Advanced (Level3)           </t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>RSA  Token number / UID</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>Reliable</t>
+  </si>
+  <si>
+    <t>Befitting Emergency</t>
+  </si>
+  <si>
+    <t>SMART</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Notice Alert</t>
+  </si>
+  <si>
+    <t>RSA QOS Training Status</t>
+  </si>
+  <si>
+    <t>RSA CTA Training Status</t>
+  </si>
+  <si>
+    <t>RSA QOPD Training Status</t>
+  </si>
+  <si>
+    <t>RSA ROC Training Status</t>
+  </si>
+  <si>
+    <t>RSA Civic Amenity Training Status</t>
+  </si>
+  <si>
+    <t>RSA FFC Training Status</t>
+  </si>
+  <si>
+    <t>Not active</t>
+  </si>
+  <si>
+    <t>Linked</t>
+  </si>
+  <si>
+    <t>Dedicated Centre</t>
+  </si>
+  <si>
+    <t>Explanation of terms</t>
+  </si>
+  <si>
+    <t>QOS: Quality of Service</t>
+  </si>
+  <si>
+    <t>QOP: Quality pf Process</t>
+  </si>
+  <si>
+    <t>QOO: Quality of Outcome</t>
+  </si>
+  <si>
+    <t>QODIL: Quality of Deep Interaction Linking</t>
+  </si>
+  <si>
+    <t>Explanation of terms:</t>
+  </si>
+  <si>
+    <t>CTA: Call To Attention issues</t>
+  </si>
+  <si>
+    <t>QOPD: Quality of Performance Dimensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROC: RADIUS OF COVERAGE </t>
+  </si>
+  <si>
+    <t>FFC: Future Forward Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B360 RS&amp;A V2R norms and best practices </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B360 Methodical-assessments </t>
+  </si>
+  <si>
+    <t>Management Accountability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMART RS&amp;A Packaging </t>
+  </si>
+  <si>
+    <t>Dedicated RS&amp;A V2R PROJECT CENTRE</t>
+  </si>
+  <si>
+    <t>RSA Role</t>
+  </si>
+  <si>
+    <t>Due Need</t>
+  </si>
+  <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>EOCC Assistance</t>
+  </si>
+  <si>
+    <t>Evaluation Review Technique</t>
+  </si>
+  <si>
+    <t>Code of SMART Packging</t>
+  </si>
+  <si>
+    <t>Critical Leverage Management</t>
+  </si>
+  <si>
+    <t>Issue Management</t>
+  </si>
+  <si>
+    <t>Critical Interaction Behaviour Modelling</t>
+  </si>
+  <si>
+    <t>Critical Interaction Dimension Modelling</t>
+  </si>
+  <si>
+    <t>Proportion Analytics</t>
+  </si>
+  <si>
+    <t>Future Analytics</t>
+  </si>
+  <si>
+    <t>Key Opinion Leadership via Case Studies-Empirical studies-Surveys</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -363,10 +549,45 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -375,9 +596,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1872,4 +2106,1628 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAC89C9-C7CD-40FD-ABAB-3C77AD7D2325}">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="34.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="28.77734375" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" customWidth="1"/>
+    <col min="12" max="12" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s">
+        <v>117</v>
+      </c>
+      <c r="N7" t="s">
+        <v>117</v>
+      </c>
+      <c r="O7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6170C4-8EDB-4544-9695-DB4864A362B3}">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="40.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="26.21875" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>130</v>
+      </c>
+      <c r="L6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4311FE66-C3F9-4451-B50A-54278E7FDCEB}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.21875" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+    <col min="11" max="12" width="26.109375" customWidth="1"/>
+    <col min="13" max="13" width="27.44140625" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D944F56-3FE3-4541-978D-D2E336D6734B}">
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.33203125" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="13" width="26.109375" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" customWidth="1"/>
+    <col min="16" max="19" width="17.77734375" customWidth="1"/>
+    <col min="20" max="20" width="23.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R2" t="s">
+        <v>111</v>
+      </c>
+      <c r="S2" t="s">
+        <v>111</v>
+      </c>
+      <c r="T2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S3" t="s">
+        <v>114</v>
+      </c>
+      <c r="T3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M4" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>115</v>
+      </c>
+      <c r="R4" t="s">
+        <v>115</v>
+      </c>
+      <c r="S4" t="s">
+        <v>115</v>
+      </c>
+      <c r="T4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L5" t="s">
+        <v>115</v>
+      </c>
+      <c r="M5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N5" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" t="s">
+        <v>115</v>
+      </c>
+      <c r="P5" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>115</v>
+      </c>
+      <c r="R5" t="s">
+        <v>115</v>
+      </c>
+      <c r="S5" t="s">
+        <v>115</v>
+      </c>
+      <c r="T5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M6" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" t="s">
+        <v>111</v>
+      </c>
+      <c r="S6" t="s">
+        <v>111</v>
+      </c>
+      <c r="T6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>152</v>
+      </c>
+      <c r="L7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M7" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" t="s">
+        <v>114</v>
+      </c>
+      <c r="O7" t="s">
+        <v>114</v>
+      </c>
+      <c r="P7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>114</v>
+      </c>
+      <c r="R7" t="s">
+        <v>114</v>
+      </c>
+      <c r="S7" t="s">
+        <v>114</v>
+      </c>
+      <c r="T7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
+++ b/v 1.00F.2026 - VSLA Case Scenario Datasets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\File additions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\SUBMISSIONS\Resubmitting via email\Corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF45C087-9952-49EB-A656-E92C6E7BB9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C0928C-E480-44D4-8877-5CB77D5888AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSLA-Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="VSLA-Training" sheetId="4" r:id="rId4"/>
     <sheet name="VSLA Process Improvement" sheetId="5" r:id="rId5"/>
     <sheet name="RS&amp;A Intelligence and CQI" sheetId="6" r:id="rId6"/>
+    <sheet name="SMART Connect" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="173">
   <si>
     <t>VSLA Transcript UID</t>
   </si>
@@ -466,9 +467,6 @@
     <t xml:space="preserve">B360 RS&amp;A V2R norms and best practices </t>
   </si>
   <si>
-    <t xml:space="preserve">B360 Methodical-assessments </t>
-  </si>
-  <si>
     <t>Management Accountability</t>
   </si>
   <si>
@@ -518,13 +516,49 @@
   </si>
   <si>
     <t>Key Opinion Leadership via Case Studies-Empirical studies-Surveys</t>
+  </si>
+  <si>
+    <t>RS&amp;A QR Code</t>
+  </si>
+  <si>
+    <t>EOCC Linked RS&amp;A QR Code</t>
+  </si>
+  <si>
+    <t>SMART Connect S&amp;A QR Code</t>
+  </si>
+  <si>
+    <t>Emergency Services QR Code</t>
+  </si>
+  <si>
+    <t>B360 Methodical-assessments using the 5R-Accentuations</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>5R(s) Accentuated methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulate response for sampling elements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record-or-review, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relate to help and improve effectiveness and responsiveness , </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduce risk, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respond and </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +569,20 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -596,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -608,11 +656,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2916,7 +2969,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4311FE66-C3F9-4451-B50A-54278E7FDCEB}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -2935,7 +2988,7 @@
     <col min="15" max="15" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2970,16 +3023,16 @@
         <v>143</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="M1" t="s">
         <v>144</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -3263,6 +3316,51 @@
       <c r="O7" t="s">
         <v>105</v>
       </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3325,34 +3423,34 @@
         <v>118</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -3387,7 +3485,7 @@
         <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L2" t="s">
         <v>111</v>
@@ -3449,7 +3547,7 @@
         <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L3" t="s">
         <v>114</v>
@@ -3511,7 +3609,7 @@
         <v>83</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L4" t="s">
         <v>115</v>
@@ -3573,7 +3671,7 @@
         <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L5" t="s">
         <v>115</v>
@@ -3635,7 +3733,7 @@
         <v>93</v>
       </c>
       <c r="K6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L6" t="s">
         <v>111</v>
@@ -3697,7 +3795,7 @@
         <v>97</v>
       </c>
       <c r="K7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L7" t="s">
         <v>114</v>
@@ -3725,6 +3823,336 @@
       </c>
       <c r="T7" t="s">
         <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E6A6B4-9821-4A4A-90D8-5142E7B6F8E0}">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="23.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
